--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X201"/>
+  <dimension ref="A1:X202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16146,6 +16146,84 @@
       <c r="X201" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="C202" t="n">
+        <v>280.31</v>
+      </c>
+      <c r="D202" t="n">
+        <v>269.39</v>
+      </c>
+      <c r="E202" t="n">
+        <v>256.76</v>
+      </c>
+      <c r="F202" t="n">
+        <v>264.41</v>
+      </c>
+      <c r="G202" t="n">
+        <v>273.01</v>
+      </c>
+      <c r="H202" t="n">
+        <v>278.87</v>
+      </c>
+      <c r="I202" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="J202" t="n">
+        <v>294.66</v>
+      </c>
+      <c r="K202" t="n">
+        <v>301.71</v>
+      </c>
+      <c r="L202" t="n">
+        <v>307.78</v>
+      </c>
+      <c r="M202" t="n">
+        <v>305.13</v>
+      </c>
+      <c r="N202" t="n">
+        <v>298.72</v>
+      </c>
+      <c r="O202" t="n">
+        <v>299.44</v>
+      </c>
+      <c r="P202" t="n">
+        <v>297.37</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>297.45</v>
+      </c>
+      <c r="R202" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="S202" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="T202" t="n">
+        <v>320.37</v>
+      </c>
+      <c r="U202" t="n">
+        <v>347.69</v>
+      </c>
+      <c r="V202" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="W202" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B202"/>
+  <dimension ref="A1:B203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18183,6 +18261,16 @@
       </c>
       <c r="B202" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>-0.96</v>
       </c>
     </row>
   </sheetData>
@@ -18351,28 +18439,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9880346496950081</v>
+        <v>-0.9755887487046095</v>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2155685741711879</v>
+        <v>0.2123051731573283</v>
       </c>
       <c r="M2" t="n">
-        <v>12.42759460428644</v>
+        <v>12.44433484721395</v>
       </c>
       <c r="N2" t="n">
-        <v>228.7538101846816</v>
+        <v>228.591412868771</v>
       </c>
       <c r="O2" t="n">
-        <v>15.12460942254978</v>
+        <v>15.11923982443466</v>
       </c>
       <c r="P2" t="n">
-        <v>293.8765539593145</v>
+        <v>293.7564711028004</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18429,28 +18517,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7657883506366594</v>
+        <v>-0.7526571601387096</v>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1762609727450322</v>
+        <v>0.1718715211991284</v>
       </c>
       <c r="M3" t="n">
-        <v>10.94468376689827</v>
+        <v>10.96384318617427</v>
       </c>
       <c r="N3" t="n">
-        <v>176.4840421096364</v>
+        <v>176.6920963100221</v>
       </c>
       <c r="O3" t="n">
-        <v>13.28472965888416</v>
+        <v>13.29255792953419</v>
       </c>
       <c r="P3" t="n">
-        <v>285.9161129166436</v>
+        <v>285.7894181224586</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18507,28 +18595,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7158516674119086</v>
+        <v>-0.7102715229323598</v>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L4" t="n">
-        <v>0.193330239257014</v>
+        <v>0.1922630909891292</v>
       </c>
       <c r="M4" t="n">
-        <v>9.590796713905041</v>
+        <v>9.578530914482544</v>
       </c>
       <c r="N4" t="n">
-        <v>137.6881363252523</v>
+        <v>137.1992517041072</v>
       </c>
       <c r="O4" t="n">
-        <v>11.73405881718906</v>
+        <v>11.71320842912424</v>
       </c>
       <c r="P4" t="n">
-        <v>282.2257749571305</v>
+        <v>282.171935569417</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18585,28 +18673,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5091098408232035</v>
+        <v>-0.5177328746488535</v>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1230012784793575</v>
+        <v>0.1273670155268908</v>
       </c>
       <c r="M5" t="n">
-        <v>8.610832262945992</v>
+        <v>8.611966515838336</v>
       </c>
       <c r="N5" t="n">
-        <v>119.0054276956912</v>
+        <v>118.8817162523387</v>
       </c>
       <c r="O5" t="n">
-        <v>10.90896088982315</v>
+        <v>10.90328924005682</v>
       </c>
       <c r="P5" t="n">
-        <v>280.1630693276483</v>
+        <v>280.2462676862404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18663,28 +18751,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3964895792144439</v>
+        <v>-0.4028559092511775</v>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08661042691609344</v>
+        <v>0.08980162375364109</v>
       </c>
       <c r="M6" t="n">
-        <v>8.302991358962476</v>
+        <v>8.295905462014712</v>
       </c>
       <c r="N6" t="n">
-        <v>106.7588473660813</v>
+        <v>106.4829987110428</v>
       </c>
       <c r="O6" t="n">
-        <v>10.33241730506861</v>
+        <v>10.3190599722573</v>
       </c>
       <c r="P6" t="n">
-        <v>282.2401554262864</v>
+        <v>282.3015802357006</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18741,28 +18829,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3142550835060958</v>
+        <v>-0.3186464333721206</v>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06479934882586513</v>
+        <v>0.06705608193522694</v>
       </c>
       <c r="M7" t="n">
-        <v>7.847815386468813</v>
+        <v>7.831350460514398</v>
       </c>
       <c r="N7" t="n">
-        <v>91.78109474058068</v>
+        <v>91.44593744602079</v>
       </c>
       <c r="O7" t="n">
-        <v>9.580245025080552</v>
+        <v>9.562736922347115</v>
       </c>
       <c r="P7" t="n">
-        <v>286.3974362645121</v>
+        <v>286.4398057029539</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18819,28 +18907,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3296196752906442</v>
+        <v>-0.3367919191430252</v>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07043634495942952</v>
+        <v>0.07376455901069889</v>
       </c>
       <c r="M8" t="n">
-        <v>7.719481742882472</v>
+        <v>7.718316167007254</v>
       </c>
       <c r="N8" t="n">
-        <v>92.33429313731733</v>
+        <v>92.19893376412755</v>
       </c>
       <c r="O8" t="n">
-        <v>9.609073479650228</v>
+        <v>9.602027586094906</v>
       </c>
       <c r="P8" t="n">
-        <v>295.8265964929745</v>
+        <v>295.8957970699415</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18897,28 +18985,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4288586195075283</v>
+        <v>-0.43695935960654</v>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1120069369563941</v>
+        <v>0.1163799432017754</v>
       </c>
       <c r="M9" t="n">
-        <v>7.716897028230028</v>
+        <v>7.717874438156295</v>
       </c>
       <c r="N9" t="n">
-        <v>93.89606452558179</v>
+        <v>93.84225733583853</v>
       </c>
       <c r="O9" t="n">
-        <v>9.689998169534491</v>
+        <v>9.687221342358113</v>
       </c>
       <c r="P9" t="n">
-        <v>304.1454605393796</v>
+        <v>304.2236196065068</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18975,28 +19063,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3590849657705813</v>
+        <v>-0.3661615570422891</v>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0862536535476669</v>
+        <v>0.08992082276909508</v>
       </c>
       <c r="M10" t="n">
-        <v>7.510956504134855</v>
+        <v>7.504480212372061</v>
       </c>
       <c r="N10" t="n">
-        <v>87.96239576041229</v>
+        <v>87.84020229697022</v>
       </c>
       <c r="O10" t="n">
-        <v>9.378826992775391</v>
+        <v>9.372310403362141</v>
       </c>
       <c r="P10" t="n">
-        <v>312.2967927170701</v>
+        <v>312.3650704010196</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -19053,28 +19141,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3671779529030338</v>
+        <v>-0.3747539580124013</v>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09865763148437845</v>
+        <v>0.1028705307542818</v>
       </c>
       <c r="M11" t="n">
-        <v>6.914471758445386</v>
+        <v>6.913556372308242</v>
       </c>
       <c r="N11" t="n">
-        <v>79.31708494282466</v>
+        <v>79.28399549830682</v>
       </c>
       <c r="O11" t="n">
-        <v>8.906013976118871</v>
+        <v>8.904156080073328</v>
       </c>
       <c r="P11" t="n">
-        <v>320.1296290496722</v>
+        <v>320.2027252710869</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -19131,28 +19219,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3997144639661322</v>
+        <v>-0.407502616563487</v>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1033315205776085</v>
+        <v>0.1075306091858531</v>
       </c>
       <c r="M12" t="n">
-        <v>7.287961055077959</v>
+        <v>7.286495487034746</v>
       </c>
       <c r="N12" t="n">
-        <v>89.27981090833087</v>
+        <v>89.21768627834362</v>
       </c>
       <c r="O12" t="n">
-        <v>9.448799442698045</v>
+        <v>9.445511435509653</v>
       </c>
       <c r="P12" t="n">
-        <v>327.3060049161825</v>
+        <v>327.381148018444</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -19209,28 +19297,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2420358563936245</v>
+        <v>-0.2498165054494483</v>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03386392616331779</v>
+        <v>0.03622869780164761</v>
       </c>
       <c r="M13" t="n">
-        <v>8.004925017107245</v>
+        <v>7.995709942074862</v>
       </c>
       <c r="N13" t="n">
-        <v>107.6254200397897</v>
+        <v>107.4712878937628</v>
       </c>
       <c r="O13" t="n">
-        <v>10.37426720495427</v>
+        <v>10.36683596348292</v>
       </c>
       <c r="P13" t="n">
-        <v>320.4346934604321</v>
+        <v>320.5097641656287</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -19287,28 +19375,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.220649252317598</v>
+        <v>-0.2297440238178665</v>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02781783386717729</v>
+        <v>0.03024754543704966</v>
       </c>
       <c r="M14" t="n">
-        <v>8.241322298132363</v>
+        <v>8.236680528784346</v>
       </c>
       <c r="N14" t="n">
-        <v>109.5679944713057</v>
+        <v>109.5438814835045</v>
       </c>
       <c r="O14" t="n">
-        <v>10.46747316554027</v>
+        <v>10.46632129659244</v>
       </c>
       <c r="P14" t="n">
-        <v>314.9397025157542</v>
+        <v>315.0274523815082</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -19365,28 +19453,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1629306345304505</v>
+        <v>-0.1699057039528505</v>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K15" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01617452577641554</v>
+        <v>0.01769002979761858</v>
       </c>
       <c r="M15" t="n">
-        <v>7.884819879792623</v>
+        <v>7.86950012387603</v>
       </c>
       <c r="N15" t="n">
-        <v>103.9791962621151</v>
+        <v>103.7683317190225</v>
       </c>
       <c r="O15" t="n">
-        <v>10.19701898900434</v>
+        <v>10.18667422268046</v>
       </c>
       <c r="P15" t="n">
-        <v>311.7065735699817</v>
+        <v>311.7738717319446</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -19443,28 +19531,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1914407005617603</v>
+        <v>-0.2014470102917545</v>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K16" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02025415347141091</v>
+        <v>0.02248096811202849</v>
       </c>
       <c r="M16" t="n">
-        <v>8.175472060377523</v>
+        <v>8.170203864154963</v>
       </c>
       <c r="N16" t="n">
-        <v>114.1622016108</v>
+        <v>114.2249019498488</v>
       </c>
       <c r="O16" t="n">
-        <v>10.68467133845492</v>
+        <v>10.68760506146483</v>
       </c>
       <c r="P16" t="n">
-        <v>313.8414132109997</v>
+        <v>313.9379579494216</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -19521,28 +19609,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1778087942540734</v>
+        <v>-0.1901742203804257</v>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K17" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01981223348598682</v>
+        <v>0.02261383679465234</v>
       </c>
       <c r="M17" t="n">
-        <v>7.87650577833441</v>
+        <v>7.882000618949708</v>
       </c>
       <c r="N17" t="n">
-        <v>100.7248815872034</v>
+        <v>101.1868674480427</v>
       </c>
       <c r="O17" t="n">
-        <v>10.03617863467981</v>
+        <v>10.0591683278511</v>
       </c>
       <c r="P17" t="n">
-        <v>316.2262723075368</v>
+        <v>316.3455787115016</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19599,28 +19687,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1780026562023187</v>
+        <v>-0.1914266276856621</v>
       </c>
       <c r="J18" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K18" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01317093535826575</v>
+        <v>0.01524289436046122</v>
       </c>
       <c r="M18" t="n">
-        <v>9.909289819621394</v>
+        <v>9.907414225900903</v>
       </c>
       <c r="N18" t="n">
-        <v>152.8736838370355</v>
+        <v>153.2481744273442</v>
       </c>
       <c r="O18" t="n">
-        <v>12.36420979428267</v>
+        <v>12.37934466873526</v>
       </c>
       <c r="P18" t="n">
-        <v>311.5816191633464</v>
+        <v>311.7111388214834</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19677,28 +19765,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2196963809002821</v>
+        <v>-0.2296498407696713</v>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02391653040296704</v>
+        <v>0.02620968663797518</v>
       </c>
       <c r="M19" t="n">
-        <v>8.772844616559507</v>
+        <v>8.771263342618367</v>
       </c>
       <c r="N19" t="n">
-        <v>126.849581358066</v>
+        <v>126.842516021412</v>
       </c>
       <c r="O19" t="n">
-        <v>11.26275194426593</v>
+        <v>11.26243828047071</v>
       </c>
       <c r="P19" t="n">
-        <v>319.2877628321561</v>
+        <v>319.3837976547244</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19755,28 +19843,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2683154566118978</v>
+        <v>-0.2752270988415037</v>
       </c>
       <c r="J20" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04396835751514416</v>
+        <v>0.04647615462607102</v>
       </c>
       <c r="M20" t="n">
-        <v>7.449871363383188</v>
+        <v>7.443422695111357</v>
       </c>
       <c r="N20" t="n">
-        <v>100.8040214961164</v>
+        <v>100.6034059219641</v>
       </c>
       <c r="O20" t="n">
-        <v>10.04012059171185</v>
+        <v>10.03012492055628</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3878099821146</v>
+        <v>335.4544961740404</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19833,28 +19921,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3504347966349726</v>
+        <v>-0.35521643903758</v>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K21" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08363922411199687</v>
+        <v>0.08642212040406083</v>
       </c>
       <c r="M21" t="n">
-        <v>7.089643442788771</v>
+        <v>7.081955384291871</v>
       </c>
       <c r="N21" t="n">
-        <v>84.43025499259933</v>
+        <v>84.14501348926571</v>
       </c>
       <c r="O21" t="n">
-        <v>9.188593744017597</v>
+        <v>9.173059112927689</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3719780228172</v>
+        <v>362.4191724602988</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19911,28 +19999,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1101209145461433</v>
+        <v>-0.1216775187478639</v>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K22" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01044799437737076</v>
+        <v>0.01271227902723049</v>
       </c>
       <c r="M22" t="n">
-        <v>6.632527479128568</v>
+        <v>6.656310749100033</v>
       </c>
       <c r="N22" t="n">
-        <v>73.96048720686835</v>
+        <v>74.4337566048395</v>
       </c>
       <c r="O22" t="n">
-        <v>8.600028325934069</v>
+        <v>8.627500020564446</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4600641512265</v>
+        <v>385.5715667290805</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19989,28 +20077,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1880593176686774</v>
+        <v>-0.1970784078992165</v>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K23" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02991166832469827</v>
+        <v>0.03285728093779294</v>
       </c>
       <c r="M23" t="n">
-        <v>6.771566943477717</v>
+        <v>6.792774780329839</v>
       </c>
       <c r="N23" t="n">
-        <v>73.8609361170351</v>
+        <v>74.00583533618385</v>
       </c>
       <c r="O23" t="n">
-        <v>8.594238542013777</v>
+        <v>8.602664432382786</v>
       </c>
       <c r="P23" t="n">
-        <v>325.1031194934604</v>
+        <v>325.1901391571133</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -20048,7 +20136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X201"/>
+  <dimension ref="A1:X202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44565,6 +44653,128 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-34.42684083199415,172.93655482498986</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>-34.4268382033559,172.93745323095118</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-34.42692294752505,172.93835355142372</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-34.427023110402274,172.93925421119684</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-34.42694041254812,172.94015086348713</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-34.426849148743834,172.94104732696715</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-34.426781922233026,172.94196985270594</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-34.426684873184456,172.94288968967123</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-34.42652627882055,172.94377798607556</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-34.42640495599576,172.94466756992054</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-34.42629244420159,172.94555798452373</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-34.42625833245449,172.94645579859517</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-34.426258026154095,172.9473568041449</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-34.42619361519942,172.9482517587389</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>-34.42615428859434,172.9491490814905</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>-34.42609563168137,172.95004457937185</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>-34.42609029023761,172.95094511155918</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>-34.42593615516938,172.95185286459488</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>-34.425664282864595,172.95275610850297</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>-34.42524573111346,172.95358166817317</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>-34.424880276453386,172.9543986425875</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>-34.425227133259085,172.95542478788735</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X202"/>
+  <dimension ref="A1:X203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16222,6 +16222,84 @@
         <v>309.84</v>
       </c>
       <c r="X202" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="C203" t="n">
+        <v>280.31</v>
+      </c>
+      <c r="D203" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="E203" t="n">
+        <v>261.06</v>
+      </c>
+      <c r="F203" t="n">
+        <v>267.15</v>
+      </c>
+      <c r="G203" t="n">
+        <v>274.16</v>
+      </c>
+      <c r="H203" t="n">
+        <v>280.61</v>
+      </c>
+      <c r="I203" t="n">
+        <v>286.08</v>
+      </c>
+      <c r="J203" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="K203" t="n">
+        <v>302.36</v>
+      </c>
+      <c r="L203" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="M203" t="n">
+        <v>306.13</v>
+      </c>
+      <c r="N203" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="O203" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="P203" t="n">
+        <v>300.16</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>300</v>
+      </c>
+      <c r="R203" t="n">
+        <v>292.91</v>
+      </c>
+      <c r="S203" t="n">
+        <v>304.09</v>
+      </c>
+      <c r="T203" t="n">
+        <v>323.21</v>
+      </c>
+      <c r="U203" t="n">
+        <v>350.58</v>
+      </c>
+      <c r="V203" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="W203" t="n">
+        <v>312.31</v>
+      </c>
+      <c r="X203" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16238,7 +16316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18271,6 +18349,16 @@
       </c>
       <c r="B203" t="n">
         <v>-0.96</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -18439,28 +18527,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9755887487046095</v>
+        <v>-0.9630981739669716</v>
       </c>
       <c r="J2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2123051731573283</v>
+        <v>0.2090418251183693</v>
       </c>
       <c r="M2" t="n">
-        <v>12.44433484721395</v>
+        <v>12.45987047032242</v>
       </c>
       <c r="N2" t="n">
-        <v>228.591412868771</v>
+        <v>228.4305607691471</v>
       </c>
       <c r="O2" t="n">
-        <v>15.11923982443466</v>
+        <v>15.11391943769541</v>
       </c>
       <c r="P2" t="n">
-        <v>293.7564711028004</v>
+        <v>293.6346377194798</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18517,28 +18605,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7526571601387096</v>
+        <v>-0.7395324695679875</v>
       </c>
       <c r="J3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1718715211991284</v>
+        <v>0.1675241653424029</v>
       </c>
       <c r="M3" t="n">
-        <v>10.96384318617427</v>
+        <v>10.98207741087894</v>
       </c>
       <c r="N3" t="n">
-        <v>176.6920963100221</v>
+        <v>176.8892426823615</v>
       </c>
       <c r="O3" t="n">
-        <v>13.29255792953419</v>
+        <v>13.29997152938161</v>
       </c>
       <c r="P3" t="n">
-        <v>285.7894181224586</v>
+        <v>285.6613995571919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18595,28 +18683,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7102715229323598</v>
+        <v>-0.7029690088843373</v>
       </c>
       <c r="J4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K4" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1922630909891292</v>
+        <v>0.1902999051208811</v>
       </c>
       <c r="M4" t="n">
-        <v>9.578530914482544</v>
+        <v>9.576502846934282</v>
       </c>
       <c r="N4" t="n">
-        <v>137.1992517041072</v>
+        <v>136.8518690522074</v>
       </c>
       <c r="O4" t="n">
-        <v>11.71320842912424</v>
+        <v>11.69837035882381</v>
       </c>
       <c r="P4" t="n">
-        <v>282.171935569417</v>
+        <v>282.1007066618683</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18673,28 +18761,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5177328746488535</v>
+        <v>-0.5223476168076208</v>
       </c>
       <c r="J5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1273670155268908</v>
+        <v>0.1304020767027695</v>
       </c>
       <c r="M5" t="n">
-        <v>8.611966515838336</v>
+        <v>8.592793762466803</v>
       </c>
       <c r="N5" t="n">
-        <v>118.8817162523387</v>
+        <v>118.4257047448623</v>
       </c>
       <c r="O5" t="n">
-        <v>10.90328924005682</v>
+        <v>10.88235749940528</v>
       </c>
       <c r="P5" t="n">
-        <v>280.2462676862404</v>
+        <v>280.291279998497</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18751,28 +18839,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4028559092511775</v>
+        <v>-0.406646756364435</v>
       </c>
       <c r="J6" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K6" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08980162375364109</v>
+        <v>0.09214129703088436</v>
       </c>
       <c r="M6" t="n">
-        <v>8.295905462014712</v>
+        <v>8.274713163178047</v>
       </c>
       <c r="N6" t="n">
-        <v>106.4829987110428</v>
+        <v>106.045274674928</v>
       </c>
       <c r="O6" t="n">
-        <v>10.3190599722573</v>
+        <v>10.29782863884072</v>
       </c>
       <c r="P6" t="n">
-        <v>282.3015802357006</v>
+        <v>282.3385562547518</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18829,28 +18917,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3186464333721206</v>
+        <v>-0.321906694140971</v>
       </c>
       <c r="J7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06705608193522694</v>
+        <v>0.06895988104064521</v>
       </c>
       <c r="M7" t="n">
-        <v>7.831350460514398</v>
+        <v>7.808934279947503</v>
       </c>
       <c r="N7" t="n">
-        <v>91.44593744602079</v>
+        <v>91.05937482955628</v>
       </c>
       <c r="O7" t="n">
-        <v>9.562736922347115</v>
+        <v>9.542503593374031</v>
       </c>
       <c r="P7" t="n">
-        <v>286.4398057029539</v>
+        <v>286.4716063693219</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18907,28 +18995,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3367919191430252</v>
+        <v>-0.342274165690077</v>
       </c>
       <c r="J8" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K8" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07376455901069889</v>
+        <v>0.07659138674154309</v>
       </c>
       <c r="M8" t="n">
-        <v>7.718316167007254</v>
+        <v>7.709072549258017</v>
       </c>
       <c r="N8" t="n">
-        <v>92.19893376412755</v>
+        <v>91.92951860916625</v>
       </c>
       <c r="O8" t="n">
-        <v>9.602027586094906</v>
+        <v>9.587988246194623</v>
       </c>
       <c r="P8" t="n">
-        <v>295.8957970699415</v>
+        <v>295.9492710420409</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18985,28 +19073,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.43695935960654</v>
+        <v>-0.442582234360459</v>
       </c>
       <c r="J9" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1163799432017754</v>
+        <v>0.1199088407537234</v>
       </c>
       <c r="M9" t="n">
-        <v>7.717874438156295</v>
+        <v>7.706341716800567</v>
       </c>
       <c r="N9" t="n">
-        <v>93.84225733583853</v>
+        <v>93.57442443806679</v>
       </c>
       <c r="O9" t="n">
-        <v>9.687221342358113</v>
+        <v>9.67338743347266</v>
       </c>
       <c r="P9" t="n">
-        <v>304.2236196065068</v>
+        <v>304.2784652697087</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -19063,28 +19151,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3661615570422891</v>
+        <v>-0.3719436463002303</v>
       </c>
       <c r="J10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08992082276909508</v>
+        <v>0.09319459063050628</v>
       </c>
       <c r="M10" t="n">
-        <v>7.504480212372061</v>
+        <v>7.491937083744352</v>
       </c>
       <c r="N10" t="n">
-        <v>87.84020229697022</v>
+        <v>87.61338144781743</v>
       </c>
       <c r="O10" t="n">
-        <v>9.372310403362141</v>
+        <v>9.360201998237935</v>
       </c>
       <c r="P10" t="n">
-        <v>312.3650704010196</v>
+        <v>312.4214690465386</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -19141,28 +19229,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3747539580124013</v>
+        <v>-0.3815962521432822</v>
       </c>
       <c r="J11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1028705307542818</v>
+        <v>0.1068983294054835</v>
       </c>
       <c r="M11" t="n">
-        <v>6.913556372308242</v>
+        <v>6.908961950104233</v>
       </c>
       <c r="N11" t="n">
-        <v>79.28399549830682</v>
+        <v>79.18281576337215</v>
       </c>
       <c r="O11" t="n">
-        <v>8.904156080073328</v>
+        <v>8.898472664641508</v>
       </c>
       <c r="P11" t="n">
-        <v>320.2027252710869</v>
+        <v>320.2694651818716</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -19219,28 +19307,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.407502616563487</v>
+        <v>-0.4141543638504023</v>
       </c>
       <c r="J12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1075306091858531</v>
+        <v>0.111399531773905</v>
       </c>
       <c r="M12" t="n">
-        <v>7.286495487034746</v>
+        <v>7.279359649140008</v>
       </c>
       <c r="N12" t="n">
-        <v>89.21768627834362</v>
+        <v>89.05133045981221</v>
       </c>
       <c r="O12" t="n">
-        <v>9.445511435509653</v>
+        <v>9.436701248837551</v>
       </c>
       <c r="P12" t="n">
-        <v>327.381148018444</v>
+        <v>327.4460293304718</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -19297,28 +19385,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2498165054494483</v>
+        <v>-0.2565759365782895</v>
       </c>
       <c r="J13" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K13" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03622869780164761</v>
+        <v>0.03842531409036087</v>
       </c>
       <c r="M13" t="n">
-        <v>7.995709942074862</v>
+        <v>7.982244422506062</v>
       </c>
       <c r="N13" t="n">
-        <v>107.4712878937628</v>
+        <v>107.2235539357572</v>
       </c>
       <c r="O13" t="n">
-        <v>10.36683596348292</v>
+        <v>10.35488068186965</v>
       </c>
       <c r="P13" t="n">
-        <v>320.5097641656287</v>
+        <v>320.5756958285864</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -19375,28 +19463,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2297440238178665</v>
+        <v>-0.2370250880767527</v>
       </c>
       <c r="J14" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K14" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03024754543704966</v>
+        <v>0.03236299528804731</v>
       </c>
       <c r="M14" t="n">
-        <v>8.236680528784346</v>
+        <v>8.225866507077516</v>
       </c>
       <c r="N14" t="n">
-        <v>109.5438814835045</v>
+        <v>109.3314601384924</v>
       </c>
       <c r="O14" t="n">
-        <v>10.46632129659244</v>
+        <v>10.45616852094937</v>
       </c>
       <c r="P14" t="n">
-        <v>315.0274523815082</v>
+        <v>315.0984720672687</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -19453,28 +19541,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1699057039528505</v>
+        <v>-0.1751289394724508</v>
       </c>
       <c r="J15" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K15" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01769002979761858</v>
+        <v>0.01893577434571803</v>
       </c>
       <c r="M15" t="n">
-        <v>7.86950012387603</v>
+        <v>7.848512586829221</v>
       </c>
       <c r="N15" t="n">
-        <v>103.7683317190225</v>
+        <v>103.4243885355201</v>
       </c>
       <c r="O15" t="n">
-        <v>10.18667422268046</v>
+        <v>10.16977819500111</v>
       </c>
       <c r="P15" t="n">
-        <v>311.7738717319446</v>
+        <v>311.8248193039018</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -19531,28 +19619,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2014470102917545</v>
+        <v>-0.2088308199960269</v>
       </c>
       <c r="J16" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K16" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02248096811202849</v>
+        <v>0.02429411238047163</v>
       </c>
       <c r="M16" t="n">
-        <v>8.170203864154963</v>
+        <v>8.155152058061262</v>
       </c>
       <c r="N16" t="n">
-        <v>114.2249019498488</v>
+        <v>113.9986828717665</v>
       </c>
       <c r="O16" t="n">
-        <v>10.68760506146483</v>
+        <v>10.67701657167238</v>
       </c>
       <c r="P16" t="n">
-        <v>313.9379579494216</v>
+        <v>314.0099798168667</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -19609,28 +19697,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1901742203804257</v>
+        <v>-0.200099954795673</v>
       </c>
       <c r="J17" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K17" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02261383679465234</v>
+        <v>0.02508130198991976</v>
       </c>
       <c r="M17" t="n">
-        <v>7.882000618949708</v>
+        <v>7.877807395416821</v>
       </c>
       <c r="N17" t="n">
-        <v>101.1868674480427</v>
+        <v>101.2989771287639</v>
       </c>
       <c r="O17" t="n">
-        <v>10.0591683278511</v>
+        <v>10.06473929760547</v>
       </c>
       <c r="P17" t="n">
-        <v>316.3455787115016</v>
+        <v>316.4423945771566</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19687,28 +19775,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1914266276856621</v>
+        <v>-0.2034994799504296</v>
       </c>
       <c r="J18" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K18" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01524289436046122</v>
+        <v>0.01726788583330419</v>
       </c>
       <c r="M18" t="n">
-        <v>9.907414225900903</v>
+        <v>9.899996411051397</v>
       </c>
       <c r="N18" t="n">
-        <v>153.2481744273442</v>
+        <v>153.3964622289779</v>
       </c>
       <c r="O18" t="n">
-        <v>12.37934466873526</v>
+        <v>12.38533254414179</v>
       </c>
       <c r="P18" t="n">
-        <v>311.7111388214834</v>
+        <v>311.8288977291912</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19765,28 +19853,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2296498407696713</v>
+        <v>-0.237705293748334</v>
       </c>
       <c r="J19" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K19" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02620968663797518</v>
+        <v>0.02822535101990542</v>
       </c>
       <c r="M19" t="n">
-        <v>8.771263342618367</v>
+        <v>8.760974748069588</v>
       </c>
       <c r="N19" t="n">
-        <v>126.842516021412</v>
+        <v>126.6183580642427</v>
       </c>
       <c r="O19" t="n">
-        <v>11.26243828047071</v>
+        <v>11.25248230677315</v>
       </c>
       <c r="P19" t="n">
-        <v>319.3837976547244</v>
+        <v>319.4623707477314</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19843,28 +19931,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2752270988415037</v>
+        <v>-0.2794869628517914</v>
       </c>
       <c r="J20" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K20" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04647615462607102</v>
+        <v>0.0482811465482339</v>
       </c>
       <c r="M20" t="n">
-        <v>7.443422695111357</v>
+        <v>7.425297536930858</v>
       </c>
       <c r="N20" t="n">
-        <v>100.6034059219641</v>
+        <v>100.2182841642831</v>
       </c>
       <c r="O20" t="n">
-        <v>10.03012492055628</v>
+        <v>10.01090825870875</v>
       </c>
       <c r="P20" t="n">
-        <v>335.4544961740404</v>
+        <v>335.4960469958208</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19921,28 +20009,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.35521643903758</v>
+        <v>-0.3572586392529739</v>
       </c>
       <c r="J21" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K21" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08642212040406083</v>
+        <v>0.0881486950333521</v>
       </c>
       <c r="M21" t="n">
-        <v>7.081955384291871</v>
+        <v>7.058208795839728</v>
       </c>
       <c r="N21" t="n">
-        <v>84.14501348926571</v>
+        <v>83.74933505277393</v>
       </c>
       <c r="O21" t="n">
-        <v>9.173059112927689</v>
+        <v>9.151466278841546</v>
       </c>
       <c r="P21" t="n">
-        <v>362.4191724602988</v>
+        <v>362.4395446572665</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19999,28 +20087,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1216775187478639</v>
+        <v>-0.1284493752982698</v>
       </c>
       <c r="J22" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K22" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01271227902723049</v>
+        <v>0.0142378459545186</v>
       </c>
       <c r="M22" t="n">
-        <v>6.656310749100033</v>
+        <v>6.656371374409997</v>
       </c>
       <c r="N22" t="n">
-        <v>74.4337566048395</v>
+        <v>74.35062097072179</v>
       </c>
       <c r="O22" t="n">
-        <v>8.627500020564446</v>
+        <v>8.622680613980886</v>
       </c>
       <c r="P22" t="n">
-        <v>385.5715667290805</v>
+        <v>385.6376195899158</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -20077,28 +20165,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1970784078992165</v>
+        <v>-0.2037762989203319</v>
       </c>
       <c r="J23" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K23" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03285728093779294</v>
+        <v>0.03527364946804479</v>
       </c>
       <c r="M23" t="n">
-        <v>6.792774780329839</v>
+        <v>6.799175597039985</v>
       </c>
       <c r="N23" t="n">
-        <v>74.00583533618385</v>
+        <v>73.91861873886664</v>
       </c>
       <c r="O23" t="n">
-        <v>8.602664432382786</v>
+        <v>8.597593776101929</v>
       </c>
       <c r="P23" t="n">
-        <v>325.1901391571133</v>
+        <v>325.2554705562968</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -20136,7 +20224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X202"/>
+  <dimension ref="A1:X203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44775,6 +44863,128 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>-34.42684083199415,172.93655482498986</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>-34.4268382033559,172.93745323095118</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>-34.42690608610538,172.9383531819859</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-34.42698433815799,172.93925336141768</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-34.42691570651536,172.94015032183003</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-34.42683877942434,172.9410470995581</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-34.42676624670838,172.94196898985396</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-34.42666149245432,172.94288755491894</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-34.426514680634824,172.94377689155445</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-34.42639911195109,172.94466701837857</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-34.42628264419229,172.94555705956455</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-34.42624934162414,172.9464549499469</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-34.4262411234005,172.94735520856875</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-34.426176982177694,172.94825018851077</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>-34.42612920421021,172.9491467132447</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>-34.42607270510356,172.95004241468956</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>-34.42607851227539,172.95094399942477</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>-34.4259184952196,172.95185052512252</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>-34.42563913064929,172.95275027857082</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>-34.42522040714691,172.95357423202034</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>-34.42483444801273,172.95438518525077</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>-34.42520548965545,172.95541843210626</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
